--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486990_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486990_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8391</v>
+        <v>5.4214</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4945</v>
+        <v>4.0175</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3446</v>
+        <v>1.4039</v>
       </c>
       <c r="G2" t="n">
         <v>4.4969</v>
@@ -610,13 +610,13 @@
         <v>1.6427</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8632</v>
+        <v>-0.2809</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7246</v>
+        <v>-0.2016</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1386</v>
+        <v>-0.0793</v>
       </c>
       <c r="V2" t="n">
         <v>0.5893</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9529</v>
+        <v>2.7486</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5003</v>
+        <v>2.1478</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4526</v>
+        <v>0.6008</v>
       </c>
       <c r="G3" t="n">
         <v>2.815</v>
@@ -688,13 +688,13 @@
         <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2727</v>
+        <v>-1.477</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1509</v>
+        <v>-0.2017</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4236</v>
+        <v>-1.2754</v>
       </c>
       <c r="V3" t="n">
         <v>0.5893</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ASO JIMENEZ</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5306</v>
+        <v>2.3988</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9966</v>
+        <v>1.7904</v>
       </c>
       <c r="F4" t="n">
-        <v>1.534</v>
+        <v>0.6085</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1141</v>
+        <v>1.4893</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9669</v>
+        <v>0.3211</v>
       </c>
       <c r="I4" t="n">
-        <v>3.081</v>
+        <v>1.1683</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2215</v>
+        <v>2.0151</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5806</v>
+        <v>1.2653</v>
       </c>
       <c r="L4" t="n">
-        <v>1.802</v>
+        <v>0.7498</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8927</v>
+        <v>-0.5258</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3863</v>
+        <v>-0.9442</v>
       </c>
       <c r="O4" t="n">
-        <v>1.279</v>
+        <v>0.4184</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5951</v>
+        <v>-0.1172</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8018999999999999</v>
+        <v>-0.2248</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2067</v>
+        <v>0.1075</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>P. ASO JIMENEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.146</v>
+        <v>1.6798</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6858</v>
+        <v>0.2644</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4603</v>
+        <v>1.4155</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4893</v>
+        <v>2.1141</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3211</v>
+        <v>-0.9669</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1683</v>
+        <v>3.081</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0151</v>
+        <v>1.2215</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2653</v>
+        <v>-0.5806</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7498</v>
+        <v>1.802</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5258</v>
+        <v>0.8927</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9442</v>
+        <v>-0.3863</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4184</v>
+        <v>1.279</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0267</v>
+        <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.37</v>
+        <v>-0.2557</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3294</v>
+        <v>0.0696</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0407</v>
+        <v>-0.3253</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Y. KOLO</t>
+          <t>J. JIMÉNEZ JIMÉNEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1141</v>
+        <v>1.136</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0583</v>
+        <v>1.6062</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0558</v>
+        <v>-0.4702</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5789</v>
+        <v>2.4349</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.0469</v>
+        <v>0.8563</v>
       </c>
       <c r="I6" t="n">
-        <v>3.6259</v>
+        <v>1.5786</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9302</v>
+        <v>3.3072</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1615</v>
+        <v>1.5446</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0917</v>
+        <v>1.7626</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3512</v>
+        <v>-0.8723</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8854</v>
+        <v>-0.6883</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5342</v>
+        <v>-0.1839</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2414</v>
+        <v>-1.2291</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2907</v>
+        <v>-0.4689</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5322</v>
+        <v>-0.7602</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.5277</v>
+        <v>-0.4805</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1786</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. JIMÉNEZ JIMÉNEZ</t>
+          <t>Y. KOLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4896</v>
+        <v>0.802</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2265</v>
+        <v>-0.0463</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.737</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.4349</v>
+        <v>1.5789</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8563</v>
+        <v>-2.0469</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5786</v>
+        <v>3.6259</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3072</v>
+        <v>1.9302</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5446</v>
+        <v>-0.1615</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7626</v>
+        <v>2.0917</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8723</v>
+        <v>-0.3512</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6883</v>
+        <v>-1.8854</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1839</v>
+        <v>1.5342</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.2321</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8756</v>
+        <v>-0.0707</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8486</v>
+        <v>-0.3953</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.027</v>
+        <v>0.3247</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.4805</v>
+        <v>-1.5277</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.4805</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0198</v>
+        <v>0.5064</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1199</v>
+        <v>2.2904</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1396</v>
+        <v>-1.7839</v>
       </c>
       <c r="G8" t="n">
         <v>2.3514</v>
@@ -1078,13 +1078,13 @@
         <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.4246</v>
+        <v>-1.8984</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8486</v>
+        <v>-0.6781</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.576</v>
+        <v>-1.2203</v>
       </c>
       <c r="V8" t="n">
         <v>-1.1786</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.627</v>
+        <v>-1.0447</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2495</v>
+        <v>-2.7265</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6225</v>
+        <v>1.6818</v>
       </c>
       <c r="G9" t="n">
         <v>1.5952</v>
@@ -1156,13 +1156,13 @@
         <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1421</v>
+        <v>-0.5598</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7246</v>
+        <v>-0.2016</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4175</v>
+        <v>-0.3582</v>
       </c>
       <c r="V9" t="n">
         <v>0.5893</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1967</v>
+        <v>-3.6225</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4443</v>
+        <v>-2.6923</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7524</v>
+        <v>-0.9302</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1634</v>
@@ -1234,13 +1234,13 @@
         <v>1.4374</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4788</v>
+        <v>-0.9046</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0464</v>
+        <v>-0.2016</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5252</v>
+        <v>-0.703</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9384</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8519</v>
+        <v>-5.3195</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.3841</v>
+        <v>-4.3182</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4678</v>
+        <v>-1.0013</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1217</v>
@@ -1312,13 +1312,13 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4098</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2171</v>
+        <v>-0.1513</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1927</v>
+        <v>-0.7262</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.3769</v>
+        <v>4.706299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2.004</v>
+        <v>2.3334</v>
       </c>
       <c r="F12" t="n">
-        <v>2.373</v>
+        <v>2.373199999999999</v>
       </c>
       <c r="G12" t="n">
         <v>16.5906</v>
@@ -1390,13 +1390,13 @@
         <v>15.4006</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.000299999999999</v>
+        <v>-7.6709</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.984399999999999</v>
+        <v>-2.6553</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.0158</v>
+        <v>-5.015700000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-3.1868</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.8815</v>
+        <v>1.7378</v>
       </c>
       <c r="E13" t="n">
-        <v>2.8067</v>
+        <v>1.7606</v>
       </c>
       <c r="F13" t="n">
-        <v>0.07480000000000001</v>
+        <v>-0.0229</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5019</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8639</v>
+        <v>1.7202</v>
       </c>
       <c r="T13" t="n">
-        <v>1.8168</v>
+        <v>0.7708</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0471</v>
+        <v>0.9494</v>
       </c>
       <c r="V13" t="n">
         <v>1.2875</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>F. ADEBAYO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2401</v>
+        <v>1.4609</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2698</v>
+        <v>2.6653</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9702</v>
+        <v>-1.2044</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.9516</v>
+        <v>-1.121</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4505</v>
+        <v>4.3019</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4021</v>
+        <v>-5.4229</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8280999999999999</v>
+        <v>2.619</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7228</v>
+        <v>5.9084</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.8947</v>
+        <v>-3.2894</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7797</v>
+        <v>-3.7399</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2723</v>
+        <v>-1.6064</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.5074</v>
+        <v>-2.1335</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>1.6427</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>3.0801</v>
+        <v>2.6694</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4319</v>
+        <v>0.8077</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5219</v>
+        <v>0.3523</v>
       </c>
       <c r="U14" t="n">
-        <v>1.91</v>
+        <v>0.4554</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2402</v>
+        <v>0.1314</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.7207</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3646</v>
+        <v>0.3942</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3646</v>
+        <v>0.3942</v>
       </c>
       <c r="G15" t="n">
         <v>0.1395</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T15" t="n">
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2546</v>
+        <v>0.2054</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1541</v>
+        <v>-0.9854000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8995</v>
+        <v>1.1908</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6133</v>
+        <v>-1.9516</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4768</v>
+        <v>1.4505</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1365</v>
+        <v>-3.4021</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0229</v>
+        <v>0.8280999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0229</v>
+        <v>2.7228</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.8947</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6362</v>
+        <v>-2.7797</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4997</v>
+        <v>-1.2723</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1365</v>
+        <v>-1.5074</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2053</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2053</v>
+        <v>3.0801</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6625</v>
+        <v>2.3972</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1312</v>
+        <v>1.2666</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5313</v>
+        <v>1.1306</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4883</v>
+        <v>-0.0664</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0521</v>
+        <v>0.0525</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4363</v>
+        <v>-0.1189</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0614</v>
@@ -1780,13 +1780,13 @@
         <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6183</v>
+        <v>1.0402</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7514</v>
+        <v>0.856</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1331</v>
+        <v>0.1842</v>
       </c>
       <c r="V17" t="n">
         <v>1.4189</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ADEBAYO</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7951</v>
+        <v>-0.5283</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2008</v>
+        <v>-1.1563</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.996</v>
+        <v>0.6279</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.121</v>
+        <v>-1.6294</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3019</v>
+        <v>-3.8341</v>
       </c>
       <c r="I18" t="n">
-        <v>-5.4229</v>
+        <v>2.2047</v>
       </c>
       <c r="J18" t="n">
-        <v>2.619</v>
+        <v>1.0399</v>
       </c>
       <c r="K18" t="n">
-        <v>5.9084</v>
+        <v>-2.3933</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.2894</v>
+        <v>3.4332</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.7399</v>
+        <v>-2.6693</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.6064</v>
+        <v>-1.4409</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1335</v>
+        <v>-1.2284</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6427</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0267</v>
+        <v>-4.1068</v>
       </c>
       <c r="R18" t="n">
-        <v>2.6694</v>
+        <v>2.4641</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4483</v>
+        <v>1.5652</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1121</v>
+        <v>0.732</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3362</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1314</v>
+        <v>1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7207</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3033</v>
+        <v>-0.7444</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0257</v>
+        <v>0.4219</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2776</v>
+        <v>-1.1663</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2002</v>
+        <v>-1.6133</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5416</v>
+        <v>-0.4768</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7419</v>
+        <v>-1.1365</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3149</v>
+        <v>0.0229</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0122</v>
+        <v>0.0229</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6974</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5151</v>
+        <v>-1.6362</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4706</v>
+        <v>-0.4997</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0445</v>
+        <v>-1.1365</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4374</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5138</v>
+        <v>0.6635</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3139</v>
+        <v>0.399</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1999</v>
+        <v>0.2645</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7278</v>
+        <v>-0.9756</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0977</v>
+        <v>-0.8165</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3699</v>
+        <v>-0.159</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6294</v>
+        <v>-1.2002</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.8341</v>
+        <v>0.5416</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2047</v>
+        <v>-1.7419</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0399</v>
+        <v>0.3149</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.3933</v>
+        <v>1.0122</v>
       </c>
       <c r="L20" t="n">
-        <v>3.4332</v>
+        <v>-0.6974</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6693</v>
+        <v>-1.5151</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4409</v>
+        <v>-0.4706</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2284</v>
+        <v>-1.0445</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.1068</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4641</v>
+        <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3657</v>
+        <v>-0.186</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2094</v>
+        <v>-0.1047</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5750999999999999</v>
+        <v>-0.0813</v>
       </c>
       <c r="V20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0531</v>
+        <v>-1.4848</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5988</v>
+        <v>-1.9712</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5456</v>
+        <v>0.4864</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6029</v>
@@ -2092,13 +2092,13 @@
         <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2449</v>
+        <v>0.3235</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2558</v>
+        <v>0.3719</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0109</v>
+        <v>-0.0484</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7499</v>
+        <v>-3.6784</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0301</v>
+        <v>-2.3439</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.7199</v>
+        <v>-1.3345</v>
       </c>
       <c r="G22" t="n">
         <v>-5.0485</v>
@@ -2170,13 +2170,13 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2451</v>
+        <v>0.3167</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6856</v>
+        <v>0.3718</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4405</v>
+        <v>-0.0551</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5893</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.3767</v>
+        <v>-3.6796</v>
       </c>
       <c r="E23" t="n">
         <v>-2.373000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.0042</v>
+        <v>-1.3067</v>
       </c>
       <c r="G23" t="n">
         <v>-16.5907</v>
@@ -2221,13 +2221,13 @@
         <v>-16.0239</v>
       </c>
       <c r="J23" t="n">
-        <v>3.515400000000001</v>
+        <v>3.5154</v>
       </c>
       <c r="K23" t="n">
         <v>8.293099999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.777900000000001</v>
+        <v>-4.7779</v>
       </c>
       <c r="M23" t="n">
         <v>-20.1059</v>
@@ -2248,13 +2248,13 @@
         <v>16.4272</v>
       </c>
       <c r="S23" t="n">
-        <v>8.0002</v>
+        <v>8.697599999999998</v>
       </c>
       <c r="T23" t="n">
-        <v>5.0157</v>
+        <v>5.015700000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>2.984499999999999</v>
+        <v>3.681900000000001</v>
       </c>
       <c r="V23" t="n">
         <v>3.1869</v>
